--- a/Week 3/DAB_Excel_Charts_Master_Class.xlsx
+++ b/Week 3/DAB_Excel_Charts_Master_Class.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop W11\working_folder\Personales\Upright\Data_Science\instructor-dab-apr-2026\wk3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ab76ec252c957cd7/Desktop/data_bootcamp_folder/instructor_ref/instructor_ref/Week 3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3F8ADCA-175D-462A-BFB8-DAEEA068BF4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="13_ncr:1_{A3F8ADCA-175D-462A-BFB8-DAEEA068BF4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{780F9901-50FE-41A9-8614-3108AFB6728A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2630" yWindow="1750" windowWidth="19570" windowHeight="12620" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Column Chart" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,20 @@
     <sheet name="6. Scatter Plot" sheetId="6" r:id="rId6"/>
     <sheet name="7. Radar Chart" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -577,7 +590,2465 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Cumulative Financial Impact</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:areaChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'5. Area Chart'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Revenue</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="40000"/>
+                <a:lumOff val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>'5. Area Chart'!$A$2:$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>Jan</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Mar</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Apr</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Jun</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jul</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Aug</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Sep</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Oct</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Nov</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Dec</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'5. Area Chart'!$B$2:$B$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1500</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1300</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1600</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1800</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1700</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1900</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2100</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2200</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2500</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2700</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F8B6-48C5-BEC4-915DE7F66E28}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'5. Area Chart'!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Expenses</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>'5. Area Chart'!$A$2:$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>Jan</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Mar</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Apr</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Jun</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jul</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Aug</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Sep</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Oct</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Nov</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Dec</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'5. Area Chart'!$C$2:$C$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>850</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1100</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1050</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1300</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1250</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1400</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1500</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1600</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-F8B6-48C5-BEC4-915DE7F66E28}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="480021920"/>
+        <c:axId val="369926448"/>
+      </c:areaChart>
+      <c:catAx>
+        <c:axId val="480021920"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="369926448"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="369926448"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>USD ($)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="480021920"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Ad Spend vs Customer Acquisition</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Customer Growth</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'6. Scatter Plot'!$A$2:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>800</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'6. Scatter Plot'!$B$2:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>115</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-76C8-48FC-A92A-54C9BC1AF8E3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="10"/>
+        <c:axId val="20"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="10"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="20"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="20"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="10"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Ad Spend vs Customer Acquisition</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'6. Scatter Plot'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>New Customers</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'6. Scatter Plot'!$A$2:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>800</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'6. Scatter Plot'!$B$2:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>115</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D017-40DC-8F8A-22F1CEEF9E0F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="545457296"/>
+        <c:axId val="369971088"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="545457296"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Investments</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="369971088"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="369971088"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>New Leads</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="545457296"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="110"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="10"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>System Performance Metrics</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'7. Radar Chart'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Score</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'7. Radar Chart'!$A$2:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Speed</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Reliability</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Design</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Usability</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Support</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'7. Radar Chart'!$B$2:$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>70</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A06C-4779-B710-6BA3D0FBD700}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="10"/>
+        <c:axId val="100"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="10"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="100"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="0"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="100"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="10"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>System Performance Metrics</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'7. Radar Chart'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Score</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'7. Radar Chart'!$A$2:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Speed</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Reliability</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Design</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Usability</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Support</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'7. Radar Chart'!$B$2:$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>70</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E042-4AC7-B7AD-4A32B92B848D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="561459200"/>
+        <c:axId val="369977808"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="561459200"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="369977808"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="369977808"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="561459200"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Annual Product Performance</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'1. Column Chart'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'1. Column Chart'!$A$2:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Product A</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Product B</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Product C</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Product D</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Product E</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Product F</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'1. Column Chart'!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>420</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>320</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>510</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>290</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>460</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D47E-4E32-88F2-702640F8644B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'1. Column Chart'!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Units Sold</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'1. Column Chart'!$A$2:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Product A</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Product B</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Product C</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Product D</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Product E</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Product F</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'1. Column Chart'!$C$2:$C$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-D47E-4E32-88F2-702640F8644B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="386166848"/>
+        <c:axId val="1861087152"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="386166848"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Units Sold </a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1861087152"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1861087152"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Sales</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="386166848"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -914,7 +3385,528 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Revenue vs Expenses Trends </a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'2. Line Chart'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Revenue</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'2. Line Chart'!$A$2:$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>Jan</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Mar</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Apr</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Jun</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jul</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Aug</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Sep</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Oct</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Nov</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Dec</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'2. Line Chart'!$B$2:$B$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1500</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1300</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1600</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1800</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1700</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1900</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2100</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2200</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2500</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2700</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-AD3B-4A83-9453-009414D8EA5D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'2. Line Chart'!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Expenses</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'2. Line Chart'!$A$2:$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>Jan</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Mar</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Apr</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Jun</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jul</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Aug</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Sep</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Oct</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Nov</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Dec</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'2. Line Chart'!$C$2:$C$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>850</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1100</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1050</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1300</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1250</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1400</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1500</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1600</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-AD3B-4A83-9453-009414D8EA5D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="372417728"/>
+        <c:axId val="369915888"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="372417728"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="369915888"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="369915888"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="372417728"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1051,7 +4043,377 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Market Share Distribution</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'3. Pie Chart'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Share</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:explosion val="15"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-EBC4-4FBA-BFBB-74997765D2D8}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="bestFit"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'3. Pie Chart'!$A$2:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Hardware</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Software</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Services</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Support</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Research</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'3. Pie Chart'!$B$2:$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-EBC4-4FBA-BFBB-74997765D2D8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="bestFit"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1311,7 +4673,451 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Performance Comparison Unit</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'4. Bar Chart'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'4. Bar Chart'!$A$2:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Product A</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Product B</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Product C</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Product D</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Product E</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Product F</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'4. Bar Chart'!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>420</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>320</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>510</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>290</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>460</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A499-40C4-B908-98DA9D326C2B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'4. Bar Chart'!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Units Sold</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'4. Bar Chart'!$A$2:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Product A</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Product B</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Product C</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Product D</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Product E</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Product F</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'4. Bar Chart'!$C$2:$C$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-A499-40C4-B908-98DA9D326C2B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="479846064"/>
+        <c:axId val="369906768"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="479846064"/>
+        <c:scaling>
+          <c:orientation val="maxMin"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="369906768"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="369906768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="t"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="479846064"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1639,364 +5445,3869 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Ad Spend vs Customer Acquisition</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:v>Customer Growth</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'6. Scatter Plot'!$A$2:$A$9</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>200</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>300</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>400</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>500</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>600</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>700</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>800</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'6. Scatter Plot'!$B$2:$B$9</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>48</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>55</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>78</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>85</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>102</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>115</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-76C8-48FC-A92A-54C9BC1AF8E3}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="10"/>
-        <c:axId val="20"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="10"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="20"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="20"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="10"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="110"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="10"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>System Performance Metrics</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:radarChart>
-        <c:radarStyle val="marker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'7. Radar Chart'!$B$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Score</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'7. Radar Chart'!$A$2:$A$6</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>Speed</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Reliability</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Design</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Usability</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Support</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'7. Radar Chart'!$B$2:$B$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>85</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>90</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>75</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>80</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>70</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A06C-4779-B710-6BA3D0FBD700}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="10"/>
-        <c:axId val="100"/>
-      </c:radarChart>
-      <c:catAx>
-        <c:axId val="10"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="100"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="0"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="100"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="10"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="276">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2032,6 +9343,42 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>4171950</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>149225</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>130175</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1BE3D60-4D5B-01B4-2371-784838F728F2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2068,6 +9415,42 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3530600</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>155575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>254000</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>136525</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A62BEC92-C234-0CBE-6AF6-9202743FF65F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2104,6 +9487,42 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3492500</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>215900</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>174625</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC2D2260-7DA6-DAAF-4649-9359791CDA35}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2140,6 +9559,42 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3416300</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>139700</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B0430516-3497-04B1-BCA0-1ABE509C1ADC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2176,6 +9631,42 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3568700</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>292100</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C6FB6D0-D735-0675-D671-45110813DAA5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2212,6 +9703,42 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>450850</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>168275</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>146050</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>149225</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3DAB6849-D2D8-DB81-DC81-C5A204B7A9E1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2248,6 +9775,42 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3854450</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>34925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>577850</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>15875</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E23B9DB6-3258-B201-3CAA-E30458EEDA84}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2537,12 +10100,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2556,7 +10119,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -2570,7 +10133,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -2584,7 +10147,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -2598,7 +10161,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -2612,7 +10175,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2626,7 +10189,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -2646,12 +10209,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
@@ -2665,7 +10228,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -2679,7 +10242,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -2693,7 +10256,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -2707,7 +10270,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -2721,7 +10284,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -2735,7 +10298,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -2746,7 +10309,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -2757,7 +10320,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -2768,7 +10331,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -2779,7 +10342,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -2790,7 +10353,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>31</v>
       </c>
@@ -2801,7 +10364,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -2821,12 +10384,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>33</v>
       </c>
@@ -2837,7 +10400,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>35</v>
       </c>
@@ -2848,7 +10411,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>37</v>
       </c>
@@ -2859,7 +10422,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -2870,7 +10433,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -2881,7 +10444,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>43</v>
       </c>
@@ -2901,12 +10464,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2920,7 +10483,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -2934,7 +10497,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -2948,7 +10511,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -2962,7 +10525,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -2976,7 +10539,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2990,7 +10553,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -3010,12 +10573,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
@@ -3029,7 +10592,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -3043,7 +10606,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -3057,7 +10620,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -3071,7 +10634,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -3085,7 +10648,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -3099,7 +10662,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -3110,7 +10673,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -3121,7 +10684,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -3132,7 +10695,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -3143,7 +10706,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -3154,7 +10717,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>31</v>
       </c>
@@ -3165,7 +10728,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -3185,9 +10748,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.54296875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>53</v>
       </c>
@@ -3195,7 +10761,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>100</v>
       </c>
@@ -3206,7 +10772,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>200</v>
       </c>
@@ -3217,7 +10783,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>300</v>
       </c>
@@ -3228,7 +10794,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>400</v>
       </c>
@@ -3239,7 +10805,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>500</v>
       </c>
@@ -3250,7 +10816,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>600</v>
       </c>
@@ -3258,7 +10824,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>700</v>
       </c>
@@ -3266,7 +10832,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>800</v>
       </c>
@@ -3283,12 +10849,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>60</v>
       </c>
@@ -3299,7 +10865,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>62</v>
       </c>
@@ -3310,7 +10876,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>63</v>
       </c>
@@ -3321,7 +10887,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>65</v>
       </c>
@@ -3332,7 +10898,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>67</v>
       </c>
@@ -3343,7 +10909,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>41</v>
       </c>
